--- a/data/ams_weekly_data/White_Mulberry/business_report_week7.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\ams_weekly_data\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E4629C-CB7E-4E72-8A56-E0D49F8B8903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DEC2EF-BD6E-4792-A300-CC37AFAC99DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="161">
   <si>
     <t>(Parent) ASIN</t>
   </si>
@@ -93,702 +93,108 @@
     <t>Total Order Items - B2B</t>
   </si>
   <si>
-    <t>2.98%</t>
-  </si>
-  <si>
-    <t>0.88%</t>
-  </si>
-  <si>
-    <t>2.33%</t>
-  </si>
-  <si>
-    <t>₹1,999.00</t>
-  </si>
-  <si>
-    <t>0.23%</t>
-  </si>
-  <si>
-    <t>1.08%</t>
-  </si>
-  <si>
-    <t>100.00%</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
-    <t>₹0.00</t>
-  </si>
-  <si>
-    <t>0.47%</t>
-  </si>
-  <si>
-    <t>0.38%</t>
-  </si>
-  <si>
-    <t>0.48%</t>
-  </si>
-  <si>
-    <t>0.95%</t>
-  </si>
-  <si>
-    <t>3.17%</t>
-  </si>
-  <si>
-    <t>50.00%</t>
-  </si>
-  <si>
-    <t>0.79%</t>
-  </si>
-  <si>
-    <t>0.63%</t>
-  </si>
-  <si>
-    <t>75.00%</t>
-  </si>
-  <si>
-    <t>0.57%</t>
-  </si>
-  <si>
-    <t>0.36%</t>
-  </si>
-  <si>
-    <t>0.53%</t>
-  </si>
-  <si>
-    <t>0.26%</t>
-  </si>
-  <si>
-    <t>0.31%</t>
-  </si>
-  <si>
-    <t>0.12%</t>
-  </si>
-  <si>
-    <t>136</t>
-  </si>
-  <si>
-    <t>0.13%</t>
-  </si>
-  <si>
-    <t>0.22%</t>
-  </si>
-  <si>
-    <t>0.76%</t>
-  </si>
-  <si>
-    <t>0.65%</t>
-  </si>
-  <si>
-    <t>0.04%</t>
-  </si>
-  <si>
-    <t>1.37%</t>
-  </si>
-  <si>
-    <t>0.06%</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>0.33%</t>
-  </si>
-  <si>
-    <t>1.17%</t>
-  </si>
-  <si>
-    <t>0.01%</t>
-  </si>
-  <si>
-    <t>340</t>
-  </si>
-  <si>
-    <t>0.87%</t>
-  </si>
-  <si>
-    <t>0.18%</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>0.17%</t>
-  </si>
-  <si>
-    <t>0.16%</t>
-  </si>
-  <si>
-    <t>1.61%</t>
-  </si>
-  <si>
-    <t>0.19%</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t>0.44%</t>
-  </si>
-  <si>
-    <t>0.24%</t>
-  </si>
-  <si>
-    <t>0.21%</t>
-  </si>
-  <si>
-    <t>1.23%</t>
-  </si>
-  <si>
-    <t>1.18%</t>
-  </si>
-  <si>
-    <t>0.10%</t>
-  </si>
-  <si>
-    <t>0.37%</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>0.15%</t>
-  </si>
-  <si>
-    <t>412</t>
-  </si>
-  <si>
-    <t>0.40%</t>
-  </si>
-  <si>
-    <t>0.71%</t>
-  </si>
-  <si>
-    <t>0.02%</t>
-  </si>
-  <si>
-    <t>0.03%</t>
-  </si>
-  <si>
-    <t>4.55%</t>
-  </si>
-  <si>
-    <t>1.94%</t>
-  </si>
-  <si>
-    <t>0.08%</t>
-  </si>
-  <si>
-    <t>2.02%</t>
-  </si>
-  <si>
-    <t>1.38%</t>
-  </si>
-  <si>
-    <t>0.11%</t>
-  </si>
-  <si>
-    <t>0.27%</t>
-  </si>
-  <si>
-    <t>44.44%</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>0.94%</t>
-  </si>
-  <si>
-    <t>0.64%</t>
-  </si>
-  <si>
-    <t>0.29%</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>1.77%</t>
-  </si>
-  <si>
-    <t>1.27%</t>
-  </si>
-  <si>
-    <t>0.86%</t>
-  </si>
-  <si>
-    <t>4.05%</t>
-  </si>
-  <si>
-    <t>0.55%</t>
-  </si>
-  <si>
-    <t>0.07%</t>
-  </si>
-  <si>
-    <t>0.67%</t>
-  </si>
-  <si>
-    <t>1.31%</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>0.56%</t>
-  </si>
-  <si>
-    <t>1.07%</t>
-  </si>
-  <si>
-    <t>1.85%</t>
-  </si>
-  <si>
-    <t>0.68%</t>
-  </si>
-  <si>
-    <t>0.62%</t>
-  </si>
-  <si>
-    <t>2.78%</t>
-  </si>
-  <si>
-    <t>0.46%</t>
-  </si>
-  <si>
-    <t>0.58%</t>
-  </si>
-  <si>
-    <t>0.42%</t>
-  </si>
-  <si>
-    <t>0.43%</t>
-  </si>
-  <si>
-    <t>0.49%</t>
-  </si>
-  <si>
-    <t>5.88%</t>
-  </si>
-  <si>
-    <t>3.33%</t>
-  </si>
-  <si>
-    <t>1,244</t>
-  </si>
-  <si>
-    <t>1,181</t>
-  </si>
-  <si>
-    <t>0.14%</t>
-  </si>
-  <si>
-    <t>1.49%</t>
-  </si>
-  <si>
-    <t>16.67%</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>1.43%</t>
-  </si>
-  <si>
-    <t>66.67%</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>0.80%</t>
-  </si>
-  <si>
-    <t>1.79%</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>7.14%</t>
-  </si>
-  <si>
-    <t>2.70%</t>
-  </si>
-  <si>
-    <t>0.93%</t>
-  </si>
-  <si>
-    <t>5.97%</t>
-  </si>
-  <si>
-    <t>2.27%</t>
-  </si>
-  <si>
     <t>B0DP2WC5VW</t>
   </si>
   <si>
     <t>White Mulberry |DIY| Wall Mounted Monitor Stand Mount | Supports 15-32 Inch Screens| 9 Kg Screen Load | VESA 75X75 &amp; 100X100 | Spring Assisted Wall Mounted Monitor Mount | Black - (Single Screen)</t>
   </si>
   <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>2.39%</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>2.67%</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>574</t>
-  </si>
-  <si>
-    <t>898</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>159</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
     <t>B0DB5VG39T</t>
   </si>
   <si>
     <t>White Mulberry |DIY| Economical Gas Spring Monitor Arm | Desk Mounted Monitor Stand for 15-32 Inch Monitors |9Kg Screen Capacity|VESA 75X75&amp;100X100| Adjustable Metal Desk Monitor Mount-(Single Screen)</t>
   </si>
   <si>
-    <t>1,603</t>
-  </si>
-  <si>
-    <t>2,212</t>
-  </si>
-  <si>
-    <t>7.84%</t>
-  </si>
-  <si>
-    <t>43.33%</t>
-  </si>
-  <si>
     <t>B0DP32F346</t>
   </si>
   <si>
     <t>White Mulberry |DIY| Woodcraft - Premium Wooden Arm | Desk Mounted Monitor arm 15-32 Inch Monitor|9Kg Screen Capacity|Spring Assisted Premium Wooden Metal Desk Mount-(Single Screen)</t>
   </si>
   <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
     <t>B0CPFS24ML</t>
   </si>
   <si>
     <t>White Mulberry Gaming Desk, Computer Desk with Carbon Fiber Surface, Z Shaped Gaming Table, Computer Table, Workstation, Home Office Desk with Cup Holder and Headphone Holder | (117 * 67 * 71 CM)</t>
   </si>
   <si>
-    <t>9,644</t>
-  </si>
-  <si>
-    <t>36.96%</t>
-  </si>
-  <si>
-    <t>33.53%</t>
-  </si>
-  <si>
-    <t>14,042</t>
-  </si>
-  <si>
-    <t>37.59%</t>
-  </si>
-  <si>
-    <t>34.91%</t>
-  </si>
-  <si>
-    <t>75.80%</t>
-  </si>
-  <si>
-    <t>91.83%</t>
-  </si>
-  <si>
-    <t>₹23,997.00</t>
-  </si>
-  <si>
     <t>B0BFWD6SNF</t>
   </si>
   <si>
     <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Carbon Fibre</t>
   </si>
   <si>
-    <t>4.53%</t>
-  </si>
-  <si>
-    <t>6.56%</t>
-  </si>
-  <si>
-    <t>1,633</t>
-  </si>
-  <si>
-    <t>4.37%</t>
-  </si>
-  <si>
-    <t>7.42%</t>
-  </si>
-  <si>
-    <t>45.66%</t>
-  </si>
-  <si>
-    <t>1.82%</t>
-  </si>
-  <si>
-    <t>₹8,315.01</t>
-  </si>
-  <si>
     <t>B0BFW59TRG</t>
   </si>
   <si>
     <t>White Mulberry L-Shape Corner Desk | Monitor Raising Shelf | Made of P2 Grade Melamine Particle Board &amp; Sturdy Steel Leg | Suitable for Office, Home, Gaming, Streaming | Black |L(130+130)*B45*H77cm</t>
   </si>
   <si>
-    <t>698</t>
-  </si>
-  <si>
-    <t>4.18%</t>
-  </si>
-  <si>
-    <t>983</t>
-  </si>
-  <si>
-    <t>2.63%</t>
-  </si>
-  <si>
-    <t>3.20%</t>
-  </si>
-  <si>
-    <t>74.17%</t>
-  </si>
-  <si>
-    <t>2.15%</t>
-  </si>
-  <si>
     <t>B0BFVMDJ2K</t>
   </si>
   <si>
     <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|White</t>
   </si>
   <si>
-    <t>3.44%</t>
-  </si>
-  <si>
-    <t>6.49%</t>
-  </si>
-  <si>
-    <t>40.82%</t>
-  </si>
-  <si>
     <t>B0CPT34B2L</t>
   </si>
   <si>
     <t>White Mulberry Wooden Motorized Electronic Height Adjustable | Ergonomic Spacious Design Desk | Motor&amp;Memory Preset Controller|Sit Stand Desk for Office, Home &amp; Study Table| 1200mmx600mm | Black</t>
   </si>
   <si>
-    <t>49.25%</t>
-  </si>
-  <si>
     <t>B0DQ1PKNSP</t>
   </si>
   <si>
     <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - White</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>299</t>
-  </si>
-  <si>
-    <t>1.35%</t>
-  </si>
-  <si>
-    <t>73.78%</t>
-  </si>
-  <si>
     <t>B0DQ51R95T</t>
   </si>
   <si>
     <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-Black</t>
   </si>
   <si>
-    <t>1.55%</t>
-  </si>
-  <si>
     <t>B0BF4S7V8C</t>
   </si>
   <si>
     <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | White</t>
   </si>
   <si>
-    <t>55.15%</t>
-  </si>
-  <si>
-    <t>5.56%</t>
-  </si>
-  <si>
-    <t>₹12,869.01</t>
-  </si>
-  <si>
     <t>B0BFVNS8HS</t>
   </si>
   <si>
     <t>White Mulberry L-Shape Corner Desk |DIY Assembly| Monitor Raising Shelf | Engineered Wood &amp; Sturdy Steel Leg|Perfect for Office Home Gaming Study Desk Computer Table|L(130+130)*45 * 77cm|Industrial</t>
   </si>
   <si>
-    <t>556</t>
-  </si>
-  <si>
-    <t>2.13%</t>
-  </si>
-  <si>
-    <t>3.10%</t>
-  </si>
-  <si>
-    <t>729</t>
-  </si>
-  <si>
-    <t>1.95%</t>
-  </si>
-  <si>
-    <t>2.36%</t>
-  </si>
-  <si>
-    <t>31.46%</t>
-  </si>
-  <si>
     <t>B0BMQQQ7YD</t>
   </si>
   <si>
     <t>White Mulberry Motorized Height Adjustable Sit-Stand Desk | Electronic Height Adjustable | Motor &amp; Memory Preset Controller | Office, Workstation or Home | Carbon Fibre | 120 * 60*H(75-118) cm</t>
   </si>
   <si>
-    <t>82.50%</t>
-  </si>
-  <si>
     <t>B0CPT3Q25C</t>
   </si>
   <si>
     <t>White Mulberry Wooden Motorized Electronic Height Adjustable | Ergonomic Spacious Design Desk | Motor&amp;Memory Preset Controller|Sit Stand Desk for Office Home &amp; Study Table| 1200mmx600mm | Carbon Fibre</t>
   </si>
   <si>
-    <t>624</t>
-  </si>
-  <si>
-    <t>4.65%</t>
-  </si>
-  <si>
-    <t>836</t>
-  </si>
-  <si>
-    <t>2.24%</t>
-  </si>
-  <si>
-    <t>4.97%</t>
-  </si>
-  <si>
-    <t>74.10%</t>
-  </si>
-  <si>
-    <t>2.56%</t>
-  </si>
-  <si>
-    <t>₹15,344.01</t>
-  </si>
-  <si>
     <t>B0DQ4YWSMC</t>
   </si>
   <si>
     <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-White</t>
   </si>
   <si>
-    <t>1.67%</t>
-  </si>
-  <si>
-    <t>474</t>
-  </si>
-  <si>
-    <t>56.73%</t>
-  </si>
-  <si>
     <t>B0DQ4ZK2WQ</t>
   </si>
   <si>
     <t>White Mulberry |120X60CM Table Top|Motorized Sit Stand Desk|Multi-Purpose Electric Height Adjustable Ergonomic Desk - Office Work study Table|3 Year Warranty|Digital screen Advance Memory Preset-Brown</t>
   </si>
   <si>
-    <t>54.81%</t>
-  </si>
-  <si>
     <t>B0BF4T7SWK</t>
   </si>
   <si>
     <t>White Mulberry Alloy Steel Manual Height Adjustable Desk | Ergonomic Design | Ecofriendly Desk | Sit Stand Desk for Office, Home &amp; Study Table| 1200Mm X 600Mm | Black</t>
   </si>
   <si>
-    <t>436</t>
-  </si>
-  <si>
-    <t>29.55%</t>
-  </si>
-  <si>
     <t>B0BMV1WPHL</t>
   </si>
   <si>
@@ -801,201 +207,78 @@
     <t>White Mulberry Motorized Height Adjustable Desk with USB Charging,Drawer|Spacious Ergonomic Design|Preset Height Controller|Sit Stand Desk for Office,Home Study,Workstation Table|1200X600mm|White</t>
   </si>
   <si>
-    <t>60.83%</t>
-  </si>
-  <si>
     <t>B0CPT2NY5M</t>
   </si>
   <si>
     <t>White Mulberry Wooden Motorized Electronic Height Adjustable | Ergonomic Spacious Design Desk | Motor&amp;Memory Preset Controller|Sit Stand Desk for Office, Home &amp; Study Table| 1200mmx600mm | White</t>
   </si>
   <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>82.98%</t>
-  </si>
-  <si>
     <t>B0DQ1NV8D2</t>
   </si>
   <si>
     <t>White Mulberry |120X60CM Table Top|Manual Sit Stand Desk|Multi-Purpose Manual Height Adjustable Ergonomic Desk - Office Work Study Table|3 Year Warranty| 80 Kg Weight Carrying Capacity - Black</t>
   </si>
   <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>586</t>
-  </si>
-  <si>
-    <t>1.57%</t>
-  </si>
-  <si>
     <t>B0DQPK7MFH</t>
   </si>
   <si>
     <t>White Mulberry L-Shape Corner Desk with Shelf|DIY Assembly| Monitor Raising Shelf |Engineered Wood &amp; Sturdy Steel Leg|Perfect for Computer Table Office Home Gaming Study Desk|L(130+130)*45*77cm|White</t>
   </si>
   <si>
-    <t>2.03%</t>
-  </si>
-  <si>
-    <t>1.41%</t>
-  </si>
-  <si>
-    <t>1.09%</t>
-  </si>
-  <si>
     <t>B0DP2VVRND</t>
   </si>
   <si>
     <t>White Mulberry |DIY| Height Adjustable Monitor Stand Mount | Supports 17-32 Inch Screens| 10 Kg Screen Load | VESA 75X75 &amp; 100X100 | Freestanding Monitor Mount | Black - (Single Screen)</t>
   </si>
   <si>
-    <t>1,376</t>
-  </si>
-  <si>
-    <t>4.14%</t>
-  </si>
-  <si>
-    <t>1,937</t>
-  </si>
-  <si>
-    <t>4.12%</t>
-  </si>
-  <si>
-    <t>88.95%</t>
-  </si>
-  <si>
-    <t>2.47%</t>
-  </si>
-  <si>
-    <t>8.25%</t>
-  </si>
-  <si>
-    <t>12.49%</t>
-  </si>
-  <si>
-    <t>8.94%</t>
-  </si>
-  <si>
-    <t>13.31%</t>
-  </si>
-  <si>
-    <t>24.05%</t>
-  </si>
-  <si>
-    <t>8.17%</t>
-  </si>
-  <si>
     <t>B0FN4D3C89</t>
   </si>
   <si>
     <t>White Mulberry Economy Fixed TV Wall Mount Bracket for 13-43 Inches |45kg|LED/LCD/Smart TV's, Universal VESA Compatible 75x75,200x200 mm MAX Slim Wall Mount Stand</t>
   </si>
   <si>
-    <t>859</t>
-  </si>
-  <si>
-    <t>5.23%</t>
-  </si>
-  <si>
-    <t>₹599.00</t>
-  </si>
-  <si>
     <t>B0DB5W4TCP</t>
   </si>
   <si>
     <t>White Mulberry |DIY| Height Adjustable Monitor Arm | Desk Mounted Stand for 15-32 Inch Monitor | 10Kg Screen Load | VESA 75X75 &amp; 100X100 | Adjustable Metal Desk Monitor Mount - (Single Screen)</t>
   </si>
   <si>
-    <t>601</t>
-  </si>
-  <si>
-    <t>5.96%</t>
-  </si>
-  <si>
     <t>B0DP2Z5DQ9</t>
   </si>
   <si>
     <t>White Mulberry 10-Step Height Adjustable Single Screen Monitor Stand for 17-32 Inch Monitor, 8 kg Load, VESA 75x75/100x100, DIY Installation (Black)</t>
   </si>
   <si>
-    <t>0.98%</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>3.92%</t>
-  </si>
-  <si>
-    <t>₹2,799.00</t>
-  </si>
-  <si>
     <t>B0FN4GQ9HT</t>
   </si>
   <si>
     <t>White Mulberry Tilt TV Wall Mount Bracket for 13–43 Inch Flat Screen TVs, Low Profile Slim Design, Heavy-Duty Steel, VESA 75x75 to 200x200, Supports up to 99 lbs (45kg), Built-in Bubble Level</t>
   </si>
   <si>
-    <t>5.39%</t>
-  </si>
-  <si>
-    <t>2.99%</t>
-  </si>
-  <si>
-    <t>37.24%</t>
-  </si>
-  <si>
     <t>B0FHVWHQHR</t>
   </si>
   <si>
     <t>White Mulberry Fixed TV Wall Mount Bracket for 37–86 Inch LED, LCD &amp; Curved TVs | Heavy Duty Steel Frame, 45kg Max Load, VESA 50x50 to 600x400mm Max, Built-in Bubble Level, 1 Year Warranty</t>
   </si>
   <si>
-    <t>4.76%</t>
-  </si>
-  <si>
     <t>B0FN4HDM6Z</t>
   </si>
   <si>
     <t>White Mulberry Premium Full Motion TV Wall Mount Bracket for 23-65Inch |35kg| LED/LCD/OLED/Smart &amp; Curved TV’s, Universal Heavy Duty Wall Mount Stand with Swivel, Tilt</t>
   </si>
   <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>₹4,598.00</t>
-  </si>
-  <si>
-    <t>81.91%</t>
-  </si>
-  <si>
     <t>B0FN4DSQ6P</t>
   </si>
   <si>
     <t>White Mulberry Premium Economy Fixed TV Wall Mount Bracket for 32-65 Inches |45kg| LED/LCD/OLED/Smart &amp; Curved TV's, VESA 50x50, 400x400 MAX, Slim Wall Stand</t>
   </si>
   <si>
-    <t>97.67%</t>
-  </si>
-  <si>
     <t>B0FN4FPJ83</t>
   </si>
   <si>
     <t>White Mulberry POS Machine Stand Universal Credit Card Machine Stand – 360° Swivel &amp; +45°/-45° Tilt |Fits 2.8"-4.3" Devices, 6.5" Panel Size| Heavy-Duty Steel &amp; Bolt-Down Mount with Cable Management</t>
   </si>
   <si>
-    <t>28.57%</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
     <t>B0FN4JG97R</t>
   </si>
   <si>
@@ -1006,9 +289,6 @@
   </si>
   <si>
     <t>White Mulberry |DIY| Height Adjustable Monitor Stand Mount | Supports 17-27 Inch Screens| 10 Kg Screen Load | VESA 75X75 &amp; 100X100 | Freestanding Monitor Mount | Black - (Dual Screen)</t>
-  </si>
-  <si>
-    <t>5.65%</t>
   </si>
   <si>
     <t>B0FN4FHH5Y</t>
@@ -1281,12 +561,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1597,10 +880,10 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>329</v>
+        <v>89</v>
       </c>
       <c r="B1" t="s">
-        <v>330</v>
+        <v>90</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -1642,7 +925,7 @@
         <v>12</v>
       </c>
       <c r="P1" t="s">
-        <v>328</v>
+        <v>88</v>
       </c>
       <c r="Q1" t="s">
         <v>13</v>
@@ -1654,7 +937,7 @@
         <v>15</v>
       </c>
       <c r="T1" t="s">
-        <v>327</v>
+        <v>87</v>
       </c>
       <c r="U1" t="s">
         <v>16</v>
@@ -1668,49 +951,49 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>332</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
-        <v>333</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F2" t="s">
-        <v>103</v>
+        <v>20</v>
+      </c>
+      <c r="F2" s="3">
+        <v>70</v>
       </c>
       <c r="G2">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" t="s">
-        <v>138</v>
+      <c r="H2" s="4">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1.5E-3</v>
+      </c>
+      <c r="J2" s="3">
+        <v>99</v>
       </c>
       <c r="K2">
         <v>12</v>
       </c>
-      <c r="L2" t="s">
-        <v>77</v>
-      </c>
-      <c r="M2" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" t="s">
-        <v>36</v>
+      <c r="L2" s="4">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="M2" s="4">
+        <v>1.8E-3</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0.75</v>
       </c>
       <c r="P2">
         <v>1</v>
@@ -1718,17 +1001,17 @@
       <c r="Q2">
         <v>0</v>
       </c>
-      <c r="R2" t="s">
-        <v>124</v>
-      </c>
-      <c r="S2" t="s">
-        <v>26</v>
+      <c r="R2" s="4">
+        <v>1.43E-2</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
       </c>
       <c r="T2" s="1">
         <v>2795.7627118644068</v>
       </c>
-      <c r="U2" t="s">
-        <v>27</v>
+      <c r="U2" s="1">
+        <v>0</v>
       </c>
       <c r="V2">
         <v>1</v>
@@ -1739,49 +1022,49 @@
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>334</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>335</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F3" t="s">
-        <v>156</v>
+        <v>22</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1603</v>
       </c>
       <c r="G3">
         <v>67</v>
       </c>
-      <c r="H3" t="s">
-        <v>88</v>
-      </c>
-      <c r="I3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J3" t="s">
-        <v>157</v>
+      <c r="H3" s="4">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1.43E-2</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2212</v>
       </c>
       <c r="K3">
         <v>93</v>
       </c>
-      <c r="L3" t="s">
-        <v>88</v>
-      </c>
-      <c r="M3" t="s">
-        <v>82</v>
-      </c>
-      <c r="N3" t="s">
-        <v>111</v>
-      </c>
-      <c r="O3" t="s">
-        <v>158</v>
+      <c r="L3" s="4">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="M3" s="4">
+        <v>1.38E-2</v>
+      </c>
+      <c r="N3" s="4">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="O3" s="4">
+        <v>7.8399999999999997E-2</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1789,17 +1072,17 @@
       <c r="Q3">
         <v>0</v>
       </c>
-      <c r="R3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S3" t="s">
-        <v>26</v>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0</v>
       </c>
       <c r="T3" s="1">
         <v>0</v>
       </c>
-      <c r="U3" t="s">
-        <v>27</v>
+      <c r="U3" s="1">
+        <v>0</v>
       </c>
       <c r="V3">
         <v>0</v>
@@ -1810,49 +1093,49 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>336</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>337</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F4" t="s">
-        <v>104</v>
+        <v>24</v>
+      </c>
+      <c r="F4" s="3">
+        <v>248</v>
       </c>
       <c r="G4">
         <v>22</v>
       </c>
-      <c r="H4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>55</v>
+      <c r="H4" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="I4" s="4">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="J4" s="3">
+        <v>340</v>
       </c>
       <c r="K4">
         <v>29</v>
       </c>
-      <c r="L4" t="s">
-        <v>69</v>
-      </c>
-      <c r="M4" t="s">
-        <v>114</v>
-      </c>
-      <c r="N4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" t="s">
-        <v>26</v>
+      <c r="L4" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="M4" s="4">
+        <v>4.3E-3</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1860,17 +1143,17 @@
       <c r="Q4">
         <v>0</v>
       </c>
-      <c r="R4" t="s">
-        <v>26</v>
-      </c>
-      <c r="S4" t="s">
-        <v>26</v>
+      <c r="R4" s="4">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4">
+        <v>0</v>
       </c>
       <c r="T4" s="1">
         <v>0</v>
       </c>
-      <c r="U4" t="s">
-        <v>27</v>
+      <c r="U4" s="1">
+        <v>0</v>
       </c>
       <c r="V4">
         <v>0</v>
@@ -1881,49 +1164,49 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>338</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>339</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>166</v>
-      </c>
-      <c r="F5" t="s">
-        <v>167</v>
+        <v>26</v>
+      </c>
+      <c r="F5" s="5">
+        <v>9644</v>
       </c>
       <c r="G5">
         <v>281</v>
       </c>
-      <c r="H5" t="s">
-        <v>168</v>
-      </c>
-      <c r="I5" t="s">
-        <v>169</v>
-      </c>
-      <c r="J5" t="s">
-        <v>170</v>
+      <c r="H5" s="4">
+        <v>0.36959999999999998</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.33529999999999999</v>
+      </c>
+      <c r="J5" s="5">
+        <v>14042</v>
       </c>
       <c r="K5">
         <v>414</v>
       </c>
-      <c r="L5" t="s">
-        <v>171</v>
-      </c>
-      <c r="M5" t="s">
-        <v>172</v>
-      </c>
-      <c r="N5" t="s">
-        <v>173</v>
-      </c>
-      <c r="O5" t="s">
-        <v>174</v>
+      <c r="L5" s="4">
+        <v>0.37590000000000001</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0.34910000000000002</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0.91830000000000001</v>
       </c>
       <c r="P5">
         <v>63</v>
@@ -1931,17 +1214,17 @@
       <c r="Q5">
         <v>3</v>
       </c>
-      <c r="R5" t="s">
-        <v>47</v>
-      </c>
-      <c r="S5" t="s">
-        <v>106</v>
+      <c r="R5" s="4">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="S5" s="4">
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="T5" s="1">
         <v>386392.37288135593</v>
       </c>
-      <c r="U5" t="s">
-        <v>175</v>
+      <c r="U5" s="1">
+        <v>23997</v>
       </c>
       <c r="V5">
         <v>63</v>
@@ -1952,49 +1235,49 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>340</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>341</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
-      </c>
-      <c r="F6" t="s">
-        <v>119</v>
+        <v>28</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1181</v>
       </c>
       <c r="G6">
         <v>55</v>
       </c>
-      <c r="H6" t="s">
-        <v>178</v>
-      </c>
-      <c r="I6" t="s">
-        <v>179</v>
-      </c>
-      <c r="J6" t="s">
-        <v>180</v>
+      <c r="H6" s="4">
+        <v>4.53E-2</v>
+      </c>
+      <c r="I6" s="4">
+        <v>6.5600000000000006E-2</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1633</v>
       </c>
       <c r="K6">
         <v>88</v>
       </c>
-      <c r="L6" t="s">
-        <v>181</v>
-      </c>
-      <c r="M6" t="s">
-        <v>182</v>
-      </c>
-      <c r="N6" t="s">
-        <v>183</v>
-      </c>
-      <c r="O6" t="s">
-        <v>25</v>
+      <c r="L6" s="4">
+        <v>4.3700000000000003E-2</v>
+      </c>
+      <c r="M6" s="4">
+        <v>7.4200000000000002E-2</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0.45660000000000001</v>
+      </c>
+      <c r="O6" s="4">
+        <v>1</v>
       </c>
       <c r="P6">
         <v>8</v>
@@ -2002,17 +1285,17 @@
       <c r="Q6">
         <v>1</v>
       </c>
-      <c r="R6" t="s">
-        <v>108</v>
-      </c>
-      <c r="S6" t="s">
-        <v>184</v>
+      <c r="R6" s="4">
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="S6" s="4">
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="T6" s="1">
         <v>56871.194915254237</v>
       </c>
-      <c r="U6" t="s">
-        <v>185</v>
+      <c r="U6" s="1">
+        <v>8315.01</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -2023,49 +1306,49 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>342</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s">
-        <v>343</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>186</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F7" t="s">
-        <v>188</v>
+        <v>30</v>
+      </c>
+      <c r="F7" s="3">
+        <v>698</v>
       </c>
       <c r="G7">
         <v>35</v>
       </c>
-      <c r="H7" t="s">
-        <v>143</v>
-      </c>
-      <c r="I7" t="s">
-        <v>189</v>
-      </c>
-      <c r="J7" t="s">
-        <v>190</v>
+      <c r="H7" s="4">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="I7" s="4">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="J7" s="3">
+        <v>983</v>
       </c>
       <c r="K7">
         <v>38</v>
       </c>
-      <c r="L7" t="s">
-        <v>191</v>
-      </c>
-      <c r="M7" t="s">
-        <v>192</v>
-      </c>
-      <c r="N7" t="s">
-        <v>193</v>
-      </c>
-      <c r="O7" t="s">
-        <v>25</v>
+      <c r="L7" s="4">
+        <v>2.63E-2</v>
+      </c>
+      <c r="M7" s="4">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="N7" s="4">
+        <v>0.74170000000000003</v>
+      </c>
+      <c r="O7" s="4">
+        <v>1</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -2073,17 +1356,17 @@
       <c r="Q7">
         <v>0</v>
       </c>
-      <c r="R7" t="s">
-        <v>93</v>
-      </c>
-      <c r="S7" t="s">
-        <v>26</v>
+      <c r="R7" s="4">
+        <v>8.6E-3</v>
+      </c>
+      <c r="S7" s="4">
+        <v>0</v>
       </c>
       <c r="T7" s="1">
         <v>42706.779661016953</v>
       </c>
-      <c r="U7" t="s">
-        <v>27</v>
+      <c r="U7" s="1">
+        <v>0</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -2094,49 +1377,49 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>344</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s">
-        <v>345</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>195</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>196</v>
-      </c>
-      <c r="F8" t="s">
-        <v>147</v>
+        <v>32</v>
+      </c>
+      <c r="F8" s="3">
+        <v>898</v>
       </c>
       <c r="G8">
         <v>50</v>
       </c>
-      <c r="H8" t="s">
-        <v>197</v>
-      </c>
-      <c r="I8" t="s">
-        <v>134</v>
-      </c>
-      <c r="J8" t="s">
-        <v>118</v>
+      <c r="H8" s="4">
+        <v>3.44E-2</v>
+      </c>
+      <c r="I8" s="4">
+        <v>5.9700000000000003E-2</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1244</v>
       </c>
       <c r="K8">
         <v>77</v>
       </c>
-      <c r="L8" t="s">
-        <v>117</v>
-      </c>
-      <c r="M8" t="s">
-        <v>198</v>
-      </c>
-      <c r="N8" t="s">
-        <v>199</v>
-      </c>
-      <c r="O8" t="s">
-        <v>25</v>
+      <c r="L8" s="4">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="M8" s="4">
+        <v>6.4899999999999999E-2</v>
+      </c>
+      <c r="N8" s="4">
+        <v>0.40820000000000001</v>
+      </c>
+      <c r="O8" s="4">
+        <v>1</v>
       </c>
       <c r="P8">
         <v>2</v>
@@ -2144,17 +1427,17 @@
       <c r="Q8">
         <v>0</v>
       </c>
-      <c r="R8" t="s">
-        <v>45</v>
-      </c>
-      <c r="S8" t="s">
-        <v>26</v>
+      <c r="R8" s="4">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="S8" s="4">
+        <v>0</v>
       </c>
       <c r="T8" s="1">
         <v>14235.593220338984</v>
       </c>
-      <c r="U8" t="s">
-        <v>27</v>
+      <c r="U8" s="1">
+        <v>0</v>
       </c>
       <c r="V8">
         <v>2</v>
@@ -2165,49 +1448,49 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>346</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>347</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>200</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>200</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" t="s">
-        <v>164</v>
+        <v>34</v>
+      </c>
+      <c r="F9" s="3">
+        <v>63</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" t="s">
-        <v>99</v>
+      <c r="H9" s="4">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="I9" s="4">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="J9" s="3">
+        <v>87</v>
       </c>
       <c r="K9">
         <v>2</v>
       </c>
-      <c r="L9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" t="s">
-        <v>59</v>
-      </c>
-      <c r="N9" t="s">
-        <v>202</v>
-      </c>
-      <c r="O9" t="s">
-        <v>25</v>
+      <c r="L9" s="4">
+        <v>2.3E-3</v>
+      </c>
+      <c r="M9" s="4">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="N9" s="4">
+        <v>0.49249999999999999</v>
+      </c>
+      <c r="O9" s="4">
+        <v>1</v>
       </c>
       <c r="P9">
         <v>2</v>
@@ -2215,17 +1498,17 @@
       <c r="Q9">
         <v>0</v>
       </c>
-      <c r="R9" t="s">
-        <v>32</v>
-      </c>
-      <c r="S9" t="s">
-        <v>26</v>
+      <c r="R9" s="4">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="S9" s="4">
+        <v>0</v>
       </c>
       <c r="T9" s="1">
         <v>22032.203389830509</v>
       </c>
-      <c r="U9" t="s">
-        <v>27</v>
+      <c r="U9" s="1">
+        <v>0</v>
       </c>
       <c r="V9">
         <v>2</v>
@@ -2236,49 +1519,49 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>348</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>349</v>
+        <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>203</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F10" t="s">
-        <v>205</v>
+        <v>36</v>
+      </c>
+      <c r="F10" s="3">
+        <v>230</v>
       </c>
       <c r="G10">
         <v>15</v>
       </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J10" t="s">
-        <v>206</v>
+      <c r="H10" s="4">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="J10" s="3">
+        <v>299</v>
       </c>
       <c r="K10">
         <v>16</v>
       </c>
-      <c r="L10" t="s">
-        <v>127</v>
-      </c>
-      <c r="M10" t="s">
-        <v>207</v>
-      </c>
-      <c r="N10" t="s">
-        <v>208</v>
-      </c>
-      <c r="O10" t="s">
-        <v>25</v>
+      <c r="L10" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="M10" s="4">
+        <v>1.35E-2</v>
+      </c>
+      <c r="N10" s="4">
+        <v>0.73780000000000001</v>
+      </c>
+      <c r="O10" s="4">
+        <v>1</v>
       </c>
       <c r="P10">
         <v>2</v>
@@ -2286,17 +1569,17 @@
       <c r="Q10">
         <v>0</v>
       </c>
-      <c r="R10" t="s">
-        <v>56</v>
-      </c>
-      <c r="S10" t="s">
-        <v>26</v>
+      <c r="R10" s="4">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="S10" s="4">
+        <v>0</v>
       </c>
       <c r="T10" s="1">
         <v>22879.661016949154</v>
       </c>
-      <c r="U10" t="s">
-        <v>27</v>
+      <c r="U10" s="1">
+        <v>0</v>
       </c>
       <c r="V10">
         <v>2</v>
@@ -2307,49 +1590,49 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>350</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>351</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>209</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>209</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11" t="s">
-        <v>153</v>
+        <v>38</v>
+      </c>
+      <c r="F11" s="3">
+        <v>86</v>
       </c>
       <c r="G11">
         <v>13</v>
       </c>
-      <c r="H11" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" t="s">
-        <v>211</v>
-      </c>
-      <c r="J11" t="s">
-        <v>43</v>
+      <c r="H11" s="4">
+        <v>3.3E-3</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1.55E-2</v>
+      </c>
+      <c r="J11" s="3">
+        <v>136</v>
       </c>
       <c r="K11">
         <v>21</v>
       </c>
-      <c r="L11" t="s">
-        <v>38</v>
-      </c>
-      <c r="M11" t="s">
-        <v>91</v>
-      </c>
-      <c r="N11" t="s">
-        <v>159</v>
-      </c>
-      <c r="O11" t="s">
-        <v>25</v>
+      <c r="L11" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="M11" s="4">
+        <v>1.77E-2</v>
+      </c>
+      <c r="N11" s="4">
+        <v>0.43330000000000002</v>
+      </c>
+      <c r="O11" s="4">
+        <v>1</v>
       </c>
       <c r="P11">
         <v>2</v>
@@ -2357,17 +1640,17 @@
       <c r="Q11">
         <v>0</v>
       </c>
-      <c r="R11" t="s">
-        <v>21</v>
-      </c>
-      <c r="S11" t="s">
-        <v>26</v>
+      <c r="R11" s="4">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="S11" s="4">
+        <v>0</v>
       </c>
       <c r="T11" s="1">
         <v>22032.203389830509</v>
       </c>
-      <c r="U11" t="s">
-        <v>27</v>
+      <c r="U11" s="1">
+        <v>0</v>
       </c>
       <c r="V11">
         <v>2</v>
@@ -2378,49 +1661,49 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>352</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>353</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>212</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>212</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>213</v>
-      </c>
-      <c r="F12" t="s">
-        <v>148</v>
+        <v>40</v>
+      </c>
+      <c r="F12" s="3">
+        <v>127</v>
       </c>
       <c r="G12">
         <v>18</v>
       </c>
-      <c r="H12" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12" t="s">
-        <v>194</v>
-      </c>
-      <c r="J12" t="s">
-        <v>58</v>
+      <c r="H12" s="4">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="I12" s="4">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="J12" s="3">
+        <v>175</v>
       </c>
       <c r="K12">
         <v>22</v>
       </c>
-      <c r="L12" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" t="s">
-        <v>107</v>
-      </c>
-      <c r="N12" t="s">
-        <v>214</v>
-      </c>
-      <c r="O12" t="s">
-        <v>25</v>
+      <c r="L12" s="4">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="M12" s="4">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="N12" s="4">
+        <v>0.55149999999999999</v>
+      </c>
+      <c r="O12" s="4">
+        <v>1</v>
       </c>
       <c r="P12">
         <v>1</v>
@@ -2428,17 +1711,17 @@
       <c r="Q12">
         <v>1</v>
       </c>
-      <c r="R12" t="s">
-        <v>34</v>
-      </c>
-      <c r="S12" t="s">
-        <v>215</v>
+      <c r="R12" s="4">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="S12" s="4">
+        <v>5.5599999999999997E-2</v>
       </c>
       <c r="T12" s="1">
         <v>10905.940677966102</v>
       </c>
-      <c r="U12" t="s">
-        <v>216</v>
+      <c r="U12" s="1">
+        <v>12869.01</v>
       </c>
       <c r="V12">
         <v>1</v>
@@ -2449,49 +1732,49 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>354</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>355</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>217</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>218</v>
-      </c>
-      <c r="F13" t="s">
-        <v>219</v>
+        <v>42</v>
+      </c>
+      <c r="F13" s="3">
+        <v>556</v>
       </c>
       <c r="G13">
         <v>26</v>
       </c>
-      <c r="H13" t="s">
-        <v>220</v>
-      </c>
-      <c r="I13" t="s">
-        <v>221</v>
-      </c>
-      <c r="J13" t="s">
-        <v>222</v>
+      <c r="H13" s="4">
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="I13" s="4">
+        <v>3.1E-2</v>
+      </c>
+      <c r="J13" s="3">
+        <v>729</v>
       </c>
       <c r="K13">
         <v>28</v>
       </c>
-      <c r="L13" t="s">
-        <v>223</v>
-      </c>
-      <c r="M13" t="s">
-        <v>224</v>
-      </c>
-      <c r="N13" t="s">
-        <v>225</v>
-      </c>
-      <c r="O13" t="s">
-        <v>25</v>
+      <c r="L13" s="4">
+        <v>1.95E-2</v>
+      </c>
+      <c r="M13" s="4">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="N13" s="4">
+        <v>0.31459999999999999</v>
+      </c>
+      <c r="O13" s="4">
+        <v>1</v>
       </c>
       <c r="P13">
         <v>1</v>
@@ -2499,17 +1782,17 @@
       <c r="Q13">
         <v>0</v>
       </c>
-      <c r="R13" t="s">
-        <v>57</v>
-      </c>
-      <c r="S13" t="s">
-        <v>26</v>
+      <c r="R13" s="4">
+        <v>1.8E-3</v>
+      </c>
+      <c r="S13" s="4">
+        <v>0</v>
       </c>
       <c r="T13" s="1">
         <v>7117.7966101694919</v>
       </c>
-      <c r="U13" t="s">
-        <v>27</v>
+      <c r="U13" s="1">
+        <v>0</v>
       </c>
       <c r="V13">
         <v>1</v>
@@ -2520,49 +1803,49 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>356</v>
+        <v>116</v>
       </c>
       <c r="B14" t="s">
-        <v>357</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>226</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>226</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>227</v>
-      </c>
-      <c r="F14" t="s">
-        <v>144</v>
+        <v>44</v>
+      </c>
+      <c r="F14" s="3">
+        <v>36</v>
       </c>
       <c r="G14">
         <v>3</v>
       </c>
-      <c r="H14" t="s">
-        <v>120</v>
-      </c>
-      <c r="I14" t="s">
-        <v>38</v>
-      </c>
-      <c r="J14" t="s">
-        <v>152</v>
+      <c r="H14" s="4">
+        <v>1.4E-3</v>
+      </c>
+      <c r="I14" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="J14" s="3">
+        <v>52</v>
       </c>
       <c r="K14">
         <v>5</v>
       </c>
-      <c r="L14" t="s">
-        <v>120</v>
-      </c>
-      <c r="M14" t="s">
-        <v>113</v>
-      </c>
-      <c r="N14" t="s">
-        <v>228</v>
-      </c>
-      <c r="O14" t="s">
-        <v>25</v>
+      <c r="L14" s="4">
+        <v>1.4E-3</v>
+      </c>
+      <c r="M14" s="4">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="O14" s="4">
+        <v>1</v>
       </c>
       <c r="P14">
         <v>1</v>
@@ -2570,17 +1853,17 @@
       <c r="Q14">
         <v>0</v>
       </c>
-      <c r="R14" t="s">
-        <v>110</v>
-      </c>
-      <c r="S14" t="s">
-        <v>26</v>
+      <c r="R14" s="4">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="S14" s="4">
+        <v>0</v>
       </c>
       <c r="T14" s="1">
         <v>11863.5593220339</v>
       </c>
-      <c r="U14" t="s">
-        <v>27</v>
+      <c r="U14" s="1">
+        <v>0</v>
       </c>
       <c r="V14">
         <v>1</v>
@@ -2591,49 +1874,49 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>358</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s">
-        <v>359</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>229</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>229</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>230</v>
-      </c>
-      <c r="F15" t="s">
-        <v>231</v>
+        <v>46</v>
+      </c>
+      <c r="F15" s="3">
+        <v>624</v>
       </c>
       <c r="G15">
         <v>39</v>
       </c>
-      <c r="H15" t="s">
-        <v>141</v>
-      </c>
-      <c r="I15" t="s">
-        <v>232</v>
-      </c>
-      <c r="J15" t="s">
-        <v>233</v>
+      <c r="H15" s="4">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="I15" s="4">
+        <v>4.65E-2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>836</v>
       </c>
       <c r="K15">
         <v>59</v>
       </c>
-      <c r="L15" t="s">
-        <v>234</v>
-      </c>
-      <c r="M15" t="s">
-        <v>235</v>
-      </c>
-      <c r="N15" t="s">
-        <v>236</v>
-      </c>
-      <c r="O15" t="s">
-        <v>25</v>
+      <c r="L15" s="4">
+        <v>2.24E-2</v>
+      </c>
+      <c r="M15" s="4">
+        <v>4.9700000000000001E-2</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0.74099999999999999</v>
+      </c>
+      <c r="O15" s="4">
+        <v>1</v>
       </c>
       <c r="P15">
         <v>1</v>
@@ -2641,17 +1924,17 @@
       <c r="Q15">
         <v>1</v>
       </c>
-      <c r="R15" t="s">
-        <v>60</v>
-      </c>
-      <c r="S15" t="s">
-        <v>237</v>
+      <c r="R15" s="4">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="S15" s="4">
+        <v>2.5600000000000001E-2</v>
       </c>
       <c r="T15" s="1">
         <v>13003.398305084747</v>
       </c>
-      <c r="U15" t="s">
-        <v>238</v>
+      <c r="U15" s="1">
+        <v>15344.01</v>
       </c>
       <c r="V15">
         <v>1</v>
@@ -2662,49 +1945,49 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="B16" t="s">
-        <v>361</v>
+        <v>121</v>
       </c>
       <c r="C16" t="s">
-        <v>239</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>239</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>240</v>
-      </c>
-      <c r="F16" t="s">
-        <v>63</v>
+        <v>48</v>
+      </c>
+      <c r="F16" s="3">
+        <v>389</v>
       </c>
       <c r="G16">
         <v>14</v>
       </c>
-      <c r="H16" t="s">
-        <v>121</v>
-      </c>
-      <c r="I16" t="s">
-        <v>241</v>
-      </c>
-      <c r="J16" t="s">
-        <v>242</v>
+      <c r="H16" s="4">
+        <v>1.49E-2</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1.67E-2</v>
+      </c>
+      <c r="J16" s="3">
+        <v>474</v>
       </c>
       <c r="K16">
         <v>17</v>
       </c>
-      <c r="L16" t="s">
-        <v>92</v>
-      </c>
-      <c r="M16" t="s">
-        <v>124</v>
-      </c>
-      <c r="N16" t="s">
-        <v>243</v>
-      </c>
-      <c r="O16" t="s">
-        <v>25</v>
+      <c r="L16" s="4">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="M16" s="4">
+        <v>1.43E-2</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0.56730000000000003</v>
+      </c>
+      <c r="O16" s="4">
+        <v>1</v>
       </c>
       <c r="P16">
         <v>1</v>
@@ -2712,17 +1995,17 @@
       <c r="Q16">
         <v>0</v>
       </c>
-      <c r="R16" t="s">
-        <v>40</v>
-      </c>
-      <c r="S16" t="s">
-        <v>26</v>
+      <c r="R16" s="4">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="S16" s="4">
+        <v>0</v>
       </c>
       <c r="T16" s="1">
         <v>13134.745762711866</v>
       </c>
-      <c r="U16" t="s">
-        <v>27</v>
+      <c r="U16" s="1">
+        <v>0</v>
       </c>
       <c r="V16">
         <v>1</v>
@@ -2733,49 +2016,49 @@
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>362</v>
+        <v>122</v>
       </c>
       <c r="B17" t="s">
-        <v>363</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
-        <v>244</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>244</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>245</v>
-      </c>
-      <c r="F17" t="s">
-        <v>86</v>
+        <v>50</v>
+      </c>
+      <c r="F17" s="3">
+        <v>162</v>
       </c>
       <c r="G17">
         <v>18</v>
       </c>
-      <c r="H17" t="s">
-        <v>109</v>
-      </c>
-      <c r="I17" t="s">
-        <v>194</v>
-      </c>
-      <c r="J17" t="s">
-        <v>205</v>
+      <c r="H17" s="4">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="I17" s="4">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="J17" s="3">
+        <v>230</v>
       </c>
       <c r="K17">
         <v>23</v>
       </c>
-      <c r="L17" t="s">
-        <v>109</v>
-      </c>
-      <c r="M17" t="s">
-        <v>79</v>
-      </c>
-      <c r="N17" t="s">
-        <v>246</v>
-      </c>
-      <c r="O17" t="s">
-        <v>25</v>
+      <c r="L17" s="4">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="M17" s="4">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="N17" s="4">
+        <v>0.54810000000000003</v>
+      </c>
+      <c r="O17" s="4">
+        <v>1</v>
       </c>
       <c r="P17">
         <v>1</v>
@@ -2783,17 +2066,17 @@
       <c r="Q17">
         <v>0</v>
       </c>
-      <c r="R17" t="s">
-        <v>109</v>
-      </c>
-      <c r="S17" t="s">
-        <v>26</v>
+      <c r="R17" s="4">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="S17" s="4">
+        <v>0</v>
       </c>
       <c r="T17" s="1">
         <v>11016.101694915254</v>
       </c>
-      <c r="U17" t="s">
-        <v>27</v>
+      <c r="U17" s="1">
+        <v>0</v>
       </c>
       <c r="V17">
         <v>1</v>
@@ -2804,49 +2087,49 @@
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>364</v>
+        <v>124</v>
       </c>
       <c r="B18" t="s">
-        <v>365</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>247</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>247</v>
+        <v>51</v>
       </c>
       <c r="E18" t="s">
-        <v>248</v>
-      </c>
-      <c r="F18" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="F18" s="3">
+        <v>342</v>
       </c>
       <c r="G18">
         <v>19</v>
       </c>
-      <c r="H18" t="s">
-        <v>98</v>
-      </c>
-      <c r="I18" t="s">
-        <v>135</v>
-      </c>
-      <c r="J18" t="s">
-        <v>249</v>
+      <c r="H18" s="4">
+        <v>1.3100000000000001E-2</v>
+      </c>
+      <c r="I18" s="4">
+        <v>2.2700000000000001E-2</v>
+      </c>
+      <c r="J18" s="3">
+        <v>436</v>
       </c>
       <c r="K18">
         <v>24</v>
       </c>
-      <c r="L18" t="s">
-        <v>53</v>
-      </c>
-      <c r="M18" t="s">
-        <v>81</v>
-      </c>
-      <c r="N18" t="s">
-        <v>250</v>
-      </c>
-      <c r="O18" t="s">
-        <v>25</v>
+      <c r="L18" s="4">
+        <v>1.17E-2</v>
+      </c>
+      <c r="M18" s="4">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="N18" s="4">
+        <v>0.29549999999999998</v>
+      </c>
+      <c r="O18" s="4">
+        <v>1</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -2854,17 +2137,17 @@
       <c r="Q18">
         <v>0</v>
       </c>
-      <c r="R18" t="s">
-        <v>26</v>
-      </c>
-      <c r="S18" t="s">
-        <v>26</v>
+      <c r="R18" s="4">
+        <v>0</v>
+      </c>
+      <c r="S18" s="4">
+        <v>0</v>
       </c>
       <c r="T18" s="1">
         <v>0</v>
       </c>
-      <c r="U18" t="s">
-        <v>27</v>
+      <c r="U18" s="1">
+        <v>0</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -2875,49 +2158,49 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>366</v>
+        <v>126</v>
       </c>
       <c r="B19" t="s">
-        <v>367</v>
+        <v>127</v>
       </c>
       <c r="C19" t="s">
-        <v>251</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>251</v>
+        <v>53</v>
       </c>
       <c r="E19" t="s">
-        <v>252</v>
-      </c>
-      <c r="F19" t="s">
-        <v>100</v>
+        <v>54</v>
+      </c>
+      <c r="F19" s="3">
+        <v>9</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
-      <c r="H19" t="s">
-        <v>77</v>
-      </c>
-      <c r="I19" t="s">
-        <v>42</v>
-      </c>
-      <c r="J19" t="s">
-        <v>100</v>
+      <c r="H19" s="4">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="J19" s="3">
+        <v>9</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="L19" t="s">
-        <v>76</v>
-      </c>
-      <c r="M19" t="s">
-        <v>80</v>
-      </c>
-      <c r="N19" t="s">
-        <v>85</v>
-      </c>
-      <c r="O19" t="s">
-        <v>25</v>
+      <c r="L19" s="4">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="M19" s="4">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0.44440000000000002</v>
+      </c>
+      <c r="O19" s="4">
+        <v>1</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -2925,17 +2208,17 @@
       <c r="Q19">
         <v>0</v>
       </c>
-      <c r="R19" t="s">
-        <v>26</v>
-      </c>
-      <c r="S19" t="s">
-        <v>26</v>
+      <c r="R19" s="4">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4">
+        <v>0</v>
       </c>
       <c r="T19" s="1">
         <v>0</v>
       </c>
-      <c r="U19" t="s">
-        <v>27</v>
+      <c r="U19" s="1">
+        <v>0</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -2946,49 +2229,49 @@
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>368</v>
+        <v>128</v>
       </c>
       <c r="B20" t="s">
-        <v>369</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>253</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>253</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>254</v>
-      </c>
-      <c r="F20" t="s">
-        <v>139</v>
+        <v>56</v>
+      </c>
+      <c r="F20" s="3">
+        <v>105</v>
       </c>
       <c r="G20">
         <v>39</v>
       </c>
-      <c r="H20" t="s">
-        <v>74</v>
-      </c>
-      <c r="I20" t="s">
-        <v>232</v>
-      </c>
-      <c r="J20" t="s">
-        <v>130</v>
+      <c r="H20" s="4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I20" s="4">
+        <v>4.65E-2</v>
+      </c>
+      <c r="J20" s="3">
+        <v>137</v>
       </c>
       <c r="K20">
         <v>48</v>
       </c>
-      <c r="L20" t="s">
-        <v>70</v>
-      </c>
-      <c r="M20" t="s">
-        <v>94</v>
-      </c>
-      <c r="N20" t="s">
-        <v>255</v>
-      </c>
-      <c r="O20" t="s">
-        <v>25</v>
+      <c r="L20" s="4">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="M20" s="4">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="N20" s="4">
+        <v>0.60829999999999995</v>
+      </c>
+      <c r="O20" s="4">
+        <v>1</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -2996,17 +2279,17 @@
       <c r="Q20">
         <v>0</v>
       </c>
-      <c r="R20" t="s">
-        <v>26</v>
-      </c>
-      <c r="S20" t="s">
-        <v>26</v>
+      <c r="R20" s="4">
+        <v>0</v>
+      </c>
+      <c r="S20" s="4">
+        <v>0</v>
       </c>
       <c r="T20" s="1">
         <v>0</v>
       </c>
-      <c r="U20" t="s">
-        <v>27</v>
+      <c r="U20" s="1">
+        <v>0</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -3017,49 +2300,49 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>370</v>
+        <v>130</v>
       </c>
       <c r="B21" t="s">
-        <v>371</v>
+        <v>131</v>
       </c>
       <c r="C21" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>256</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
-        <v>257</v>
-      </c>
-      <c r="F21" t="s">
-        <v>258</v>
+        <v>58</v>
+      </c>
+      <c r="F21" s="3">
+        <v>126</v>
       </c>
       <c r="G21">
         <v>8</v>
       </c>
-      <c r="H21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" t="s">
-        <v>259</v>
+      <c r="H21" s="4">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="I21" s="4">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="J21" s="3">
+        <v>165</v>
       </c>
       <c r="K21">
         <v>9</v>
       </c>
-      <c r="L21" t="s">
-        <v>64</v>
-      </c>
-      <c r="M21" t="s">
-        <v>46</v>
-      </c>
-      <c r="N21" t="s">
-        <v>260</v>
-      </c>
-      <c r="O21" t="s">
-        <v>25</v>
+      <c r="L21" s="4">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="M21" s="4">
+        <v>7.6E-3</v>
+      </c>
+      <c r="N21" s="4">
+        <v>0.82979999999999998</v>
+      </c>
+      <c r="O21" s="4">
+        <v>1</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -3067,17 +2350,17 @@
       <c r="Q21">
         <v>0</v>
       </c>
-      <c r="R21" t="s">
-        <v>26</v>
-      </c>
-      <c r="S21" t="s">
-        <v>26</v>
+      <c r="R21" s="4">
+        <v>0</v>
+      </c>
+      <c r="S21" s="4">
+        <v>0</v>
       </c>
       <c r="T21" s="1">
         <v>0</v>
       </c>
-      <c r="U21" t="s">
-        <v>27</v>
+      <c r="U21" s="1">
+        <v>0</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -3088,49 +2371,49 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="B22" t="s">
-        <v>373</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
-        <v>261</v>
+        <v>59</v>
       </c>
       <c r="D22" t="s">
-        <v>261</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>262</v>
-      </c>
-      <c r="F22" t="s">
-        <v>263</v>
+        <v>60</v>
+      </c>
+      <c r="F22" s="3">
+        <v>420</v>
       </c>
       <c r="G22">
         <v>9</v>
       </c>
-      <c r="H22" t="s">
-        <v>61</v>
-      </c>
-      <c r="I22" t="s">
-        <v>106</v>
-      </c>
-      <c r="J22" t="s">
-        <v>264</v>
+      <c r="H22" s="4">
+        <v>1.61E-2</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="J22" s="3">
+        <v>586</v>
       </c>
       <c r="K22">
         <v>11</v>
       </c>
-      <c r="L22" t="s">
-        <v>265</v>
-      </c>
-      <c r="M22" t="s">
-        <v>133</v>
-      </c>
-      <c r="N22" t="s">
-        <v>208</v>
-      </c>
-      <c r="O22" t="s">
-        <v>25</v>
+      <c r="L22" s="4">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="M22" s="4">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="N22" s="4">
+        <v>0.73780000000000001</v>
+      </c>
+      <c r="O22" s="4">
+        <v>1</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -3138,17 +2421,17 @@
       <c r="Q22">
         <v>0</v>
       </c>
-      <c r="R22" t="s">
-        <v>26</v>
-      </c>
-      <c r="S22" t="s">
-        <v>26</v>
+      <c r="R22" s="4">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4">
+        <v>0</v>
       </c>
       <c r="T22" s="1">
         <v>0</v>
       </c>
-      <c r="U22" t="s">
-        <v>27</v>
+      <c r="U22" s="1">
+        <v>0</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -3159,49 +2442,49 @@
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>374</v>
+        <v>134</v>
       </c>
       <c r="B23" t="s">
-        <v>375</v>
+        <v>135</v>
       </c>
       <c r="C23" t="s">
-        <v>266</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>266</v>
+        <v>61</v>
       </c>
       <c r="E23" t="s">
-        <v>267</v>
-      </c>
-      <c r="F23" t="s">
-        <v>129</v>
+        <v>62</v>
+      </c>
+      <c r="F23" s="3">
+        <v>184</v>
       </c>
       <c r="G23">
         <v>17</v>
       </c>
-      <c r="H23" t="s">
-        <v>75</v>
-      </c>
-      <c r="I23" t="s">
-        <v>268</v>
-      </c>
-      <c r="J23" t="s">
-        <v>126</v>
+      <c r="H23" s="4">
+        <v>7.1000000000000004E-3</v>
+      </c>
+      <c r="I23" s="4">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="J23" s="3">
+        <v>214</v>
       </c>
       <c r="K23">
         <v>21</v>
       </c>
-      <c r="L23" t="s">
-        <v>37</v>
-      </c>
-      <c r="M23" t="s">
-        <v>91</v>
-      </c>
-      <c r="N23" t="s">
-        <v>33</v>
-      </c>
-      <c r="O23" t="s">
-        <v>25</v>
+      <c r="L23" s="4">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="M23" s="4">
+        <v>1.77E-2</v>
+      </c>
+      <c r="N23" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="O23" s="4">
+        <v>1</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -3209,17 +2492,17 @@
       <c r="Q23">
         <v>0</v>
       </c>
-      <c r="R23" t="s">
-        <v>26</v>
-      </c>
-      <c r="S23" t="s">
-        <v>26</v>
+      <c r="R23" s="4">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4">
+        <v>0</v>
       </c>
       <c r="T23" s="1">
         <v>0</v>
       </c>
-      <c r="U23" t="s">
-        <v>27</v>
+      <c r="U23" s="1">
+        <v>0</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -3230,49 +2513,49 @@
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>376</v>
+        <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>377</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>271</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>271</v>
+        <v>63</v>
       </c>
       <c r="E24" t="s">
-        <v>272</v>
-      </c>
-      <c r="F24" t="s">
-        <v>273</v>
+        <v>64</v>
+      </c>
+      <c r="F24" s="5">
+        <v>1376</v>
       </c>
       <c r="G24">
         <v>93</v>
       </c>
-      <c r="H24" t="s">
-        <v>68</v>
-      </c>
-      <c r="I24" t="s">
-        <v>274</v>
-      </c>
-      <c r="J24" t="s">
-        <v>275</v>
+      <c r="H24" s="4">
+        <v>1.18E-2</v>
+      </c>
+      <c r="I24" s="4">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="J24" s="5">
+        <v>1937</v>
       </c>
       <c r="K24">
         <v>128</v>
       </c>
-      <c r="L24" t="s">
-        <v>67</v>
-      </c>
-      <c r="M24" t="s">
-        <v>276</v>
-      </c>
-      <c r="N24" t="s">
-        <v>277</v>
-      </c>
-      <c r="O24" t="s">
-        <v>131</v>
+      <c r="L24" s="4">
+        <v>1.23E-2</v>
+      </c>
+      <c r="M24" s="4">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="N24" s="4">
+        <v>0.88949999999999996</v>
+      </c>
+      <c r="O24" s="4">
+        <v>7.1400000000000005E-2</v>
       </c>
       <c r="P24">
         <v>34</v>
@@ -3280,17 +2563,17 @@
       <c r="Q24">
         <v>1</v>
       </c>
-      <c r="R24" t="s">
-        <v>278</v>
-      </c>
-      <c r="S24" t="s">
-        <v>24</v>
+      <c r="R24" s="4">
+        <v>2.47E-2</v>
+      </c>
+      <c r="S24" s="4">
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="T24" s="1">
         <v>55904.237288135599</v>
       </c>
-      <c r="U24" t="s">
-        <v>22</v>
+      <c r="U24" s="1">
+        <v>1999</v>
       </c>
       <c r="V24">
         <v>34</v>
@@ -3301,49 +2584,49 @@
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>338</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>339</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>166</v>
-      </c>
-      <c r="F25" t="s">
-        <v>167</v>
+        <v>26</v>
+      </c>
+      <c r="F25" s="5">
+        <v>9644</v>
       </c>
       <c r="G25">
         <v>281</v>
       </c>
-      <c r="H25" t="s">
-        <v>279</v>
-      </c>
-      <c r="I25" t="s">
-        <v>280</v>
-      </c>
-      <c r="J25" t="s">
-        <v>170</v>
+      <c r="H25" s="4">
+        <v>8.2500000000000004E-2</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0.1249</v>
+      </c>
+      <c r="J25" s="5">
+        <v>14042</v>
       </c>
       <c r="K25">
         <v>414</v>
       </c>
-      <c r="L25" t="s">
-        <v>281</v>
-      </c>
-      <c r="M25" t="s">
-        <v>282</v>
-      </c>
-      <c r="N25" t="s">
-        <v>283</v>
-      </c>
-      <c r="O25" t="s">
-        <v>284</v>
+      <c r="L25" s="4">
+        <v>8.9399999999999993E-2</v>
+      </c>
+      <c r="M25" s="4">
+        <v>0.1331</v>
+      </c>
+      <c r="N25" s="4">
+        <v>0.24049999999999999</v>
+      </c>
+      <c r="O25" s="4">
+        <v>8.1699999999999995E-2</v>
       </c>
       <c r="P25">
         <v>30</v>
@@ -3351,17 +2634,17 @@
       <c r="Q25">
         <v>0</v>
       </c>
-      <c r="R25" t="s">
-        <v>41</v>
-      </c>
-      <c r="S25" t="s">
-        <v>26</v>
+      <c r="R25" s="4">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="S25" s="4">
+        <v>0</v>
       </c>
       <c r="T25" s="1">
         <v>189806.77966101695</v>
       </c>
-      <c r="U25" t="s">
-        <v>27</v>
+      <c r="U25" s="1">
+        <v>0</v>
       </c>
       <c r="V25">
         <v>30</v>
@@ -3372,49 +2655,49 @@
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>378</v>
+        <v>138</v>
       </c>
       <c r="B26" t="s">
-        <v>379</v>
+        <v>139</v>
       </c>
       <c r="C26" t="s">
-        <v>285</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>65</v>
       </c>
       <c r="E26" t="s">
-        <v>286</v>
-      </c>
-      <c r="F26" t="s">
-        <v>146</v>
+        <v>66</v>
+      </c>
+      <c r="F26" s="3">
+        <v>574</v>
       </c>
       <c r="G26">
         <v>17</v>
       </c>
-      <c r="H26" t="s">
-        <v>115</v>
-      </c>
-      <c r="I26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J26" t="s">
-        <v>287</v>
+      <c r="H26" s="4">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="I26" s="4">
+        <v>7.6E-3</v>
+      </c>
+      <c r="J26" s="3">
+        <v>859</v>
       </c>
       <c r="K26">
         <v>25</v>
       </c>
-      <c r="L26" t="s">
-        <v>95</v>
-      </c>
-      <c r="M26" t="s">
-        <v>127</v>
-      </c>
-      <c r="N26" t="s">
-        <v>25</v>
-      </c>
-      <c r="O26" t="s">
-        <v>25</v>
+      <c r="L26" s="4">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="M26" s="4">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="N26" s="4">
+        <v>1</v>
+      </c>
+      <c r="O26" s="4">
+        <v>1</v>
       </c>
       <c r="P26">
         <v>30</v>
@@ -3422,17 +2705,17 @@
       <c r="Q26">
         <v>1</v>
       </c>
-      <c r="R26" t="s">
-        <v>288</v>
-      </c>
-      <c r="S26" t="s">
-        <v>116</v>
+      <c r="R26" s="4">
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="S26" s="4">
+        <v>5.8799999999999998E-2</v>
       </c>
       <c r="T26" s="1">
         <v>15228.813559322034</v>
       </c>
-      <c r="U26" t="s">
-        <v>289</v>
+      <c r="U26" s="1">
+        <v>599</v>
       </c>
       <c r="V26">
         <v>30</v>
@@ -3443,49 +2726,49 @@
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>380</v>
+        <v>140</v>
       </c>
       <c r="B27" t="s">
-        <v>381</v>
+        <v>141</v>
       </c>
       <c r="C27" t="s">
-        <v>290</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>291</v>
-      </c>
-      <c r="F27" t="s">
-        <v>249</v>
+        <v>68</v>
+      </c>
+      <c r="F27" s="3">
+        <v>436</v>
       </c>
       <c r="G27">
         <v>15</v>
       </c>
-      <c r="H27" t="s">
-        <v>70</v>
-      </c>
-      <c r="I27" t="s">
-        <v>97</v>
-      </c>
-      <c r="J27" t="s">
-        <v>292</v>
+      <c r="H27" s="4">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="I27" s="4">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="J27" s="3">
+        <v>601</v>
       </c>
       <c r="K27">
         <v>21</v>
       </c>
-      <c r="L27" t="s">
-        <v>29</v>
-      </c>
-      <c r="M27" t="s">
-        <v>108</v>
-      </c>
-      <c r="N27" t="s">
-        <v>25</v>
-      </c>
-      <c r="O27" t="s">
-        <v>25</v>
+      <c r="L27" s="4">
+        <v>3.8E-3</v>
+      </c>
+      <c r="M27" s="4">
+        <v>6.7999999999999996E-3</v>
+      </c>
+      <c r="N27" s="4">
+        <v>1</v>
+      </c>
+      <c r="O27" s="4">
+        <v>1</v>
       </c>
       <c r="P27">
         <v>26</v>
@@ -3493,17 +2776,17 @@
       <c r="Q27">
         <v>0</v>
       </c>
-      <c r="R27" t="s">
-        <v>293</v>
-      </c>
-      <c r="S27" t="s">
-        <v>26</v>
+      <c r="R27" s="4">
+        <v>5.96E-2</v>
+      </c>
+      <c r="S27" s="4">
+        <v>0</v>
       </c>
       <c r="T27" s="1">
         <v>36333.898305084746</v>
       </c>
-      <c r="U27" t="s">
-        <v>27</v>
+      <c r="U27" s="1">
+        <v>0</v>
       </c>
       <c r="V27">
         <v>13</v>
@@ -3514,49 +2797,49 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>382</v>
+        <v>142</v>
       </c>
       <c r="B28" t="s">
-        <v>383</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
-        <v>294</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>294</v>
+        <v>69</v>
       </c>
       <c r="E28" t="s">
-        <v>295</v>
-      </c>
-      <c r="F28" t="s">
-        <v>149</v>
+        <v>70</v>
+      </c>
+      <c r="F28" s="3">
+        <v>306</v>
       </c>
       <c r="G28">
         <v>22</v>
       </c>
-      <c r="H28" t="s">
-        <v>40</v>
-      </c>
-      <c r="I28" t="s">
-        <v>296</v>
-      </c>
-      <c r="J28" t="s">
-        <v>297</v>
+      <c r="H28" s="4">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="I28" s="4">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="J28" s="3">
+        <v>401</v>
       </c>
       <c r="K28">
         <v>34</v>
       </c>
-      <c r="L28" t="s">
-        <v>40</v>
-      </c>
-      <c r="M28" t="s">
-        <v>270</v>
-      </c>
-      <c r="N28" t="s">
-        <v>25</v>
-      </c>
-      <c r="O28" t="s">
-        <v>25</v>
+      <c r="L28" s="4">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="M28" s="4">
+        <v>1.09E-2</v>
+      </c>
+      <c r="N28" s="4">
+        <v>1</v>
+      </c>
+      <c r="O28" s="4">
+        <v>1</v>
       </c>
       <c r="P28">
         <v>12</v>
@@ -3564,17 +2847,17 @@
       <c r="Q28">
         <v>1</v>
       </c>
-      <c r="R28" t="s">
-        <v>298</v>
-      </c>
-      <c r="S28" t="s">
-        <v>78</v>
+      <c r="R28" s="4">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="S28" s="4">
+        <v>4.5499999999999999E-2</v>
       </c>
       <c r="T28" s="1">
         <v>26092.372881355932</v>
       </c>
-      <c r="U28" t="s">
-        <v>299</v>
+      <c r="U28" s="1">
+        <v>2799</v>
       </c>
       <c r="V28">
         <v>12</v>
@@ -3585,49 +2868,49 @@
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>384</v>
+        <v>144</v>
       </c>
       <c r="B29" t="s">
-        <v>385</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>300</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
-        <v>300</v>
+        <v>71</v>
       </c>
       <c r="E29" t="s">
-        <v>301</v>
-      </c>
-      <c r="F29" t="s">
-        <v>151</v>
+        <v>72</v>
+      </c>
+      <c r="F29" s="3">
+        <v>204</v>
       </c>
       <c r="G29">
         <v>9</v>
       </c>
-      <c r="H29" t="s">
-        <v>59</v>
-      </c>
-      <c r="I29" t="s">
-        <v>74</v>
-      </c>
-      <c r="J29" t="s">
-        <v>206</v>
+      <c r="H29" s="4">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="I29" s="4">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J29" s="3">
+        <v>299</v>
       </c>
       <c r="K29">
         <v>9</v>
       </c>
-      <c r="L29" t="s">
-        <v>62</v>
-      </c>
-      <c r="M29" t="s">
-        <v>89</v>
-      </c>
-      <c r="N29" t="s">
-        <v>25</v>
-      </c>
-      <c r="O29" t="s">
-        <v>25</v>
+      <c r="L29" s="4">
+        <v>1.9E-3</v>
+      </c>
+      <c r="M29" s="4">
+        <v>2.8999999999999998E-3</v>
+      </c>
+      <c r="N29" s="4">
+        <v>1</v>
+      </c>
+      <c r="O29" s="4">
+        <v>1</v>
       </c>
       <c r="P29">
         <v>11</v>
@@ -3635,17 +2918,17 @@
       <c r="Q29">
         <v>0</v>
       </c>
-      <c r="R29" t="s">
-        <v>302</v>
-      </c>
-      <c r="S29" t="s">
-        <v>26</v>
+      <c r="R29" s="4">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="S29" s="4">
+        <v>0</v>
       </c>
       <c r="T29" s="1">
         <v>7914.406779661017</v>
       </c>
-      <c r="U29" t="s">
-        <v>27</v>
+      <c r="U29" s="1">
+        <v>0</v>
       </c>
       <c r="V29">
         <v>11</v>
@@ -3656,49 +2939,49 @@
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>334</v>
+        <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>335</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>155</v>
-      </c>
-      <c r="F30" t="s">
-        <v>156</v>
+        <v>22</v>
+      </c>
+      <c r="F30" s="5">
+        <v>1603</v>
       </c>
       <c r="G30">
         <v>67</v>
       </c>
-      <c r="H30" t="s">
-        <v>49</v>
-      </c>
-      <c r="I30" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" t="s">
-        <v>157</v>
+      <c r="H30" s="4">
+        <v>1.37E-2</v>
+      </c>
+      <c r="I30" s="4">
+        <v>2.98E-2</v>
+      </c>
+      <c r="J30" s="5">
+        <v>2212</v>
       </c>
       <c r="K30">
         <v>93</v>
       </c>
-      <c r="L30" t="s">
-        <v>269</v>
-      </c>
-      <c r="M30" t="s">
-        <v>303</v>
-      </c>
-      <c r="N30" t="s">
-        <v>304</v>
-      </c>
-      <c r="O30" t="s">
-        <v>26</v>
+      <c r="L30" s="4">
+        <v>1.41E-2</v>
+      </c>
+      <c r="M30" s="4">
+        <v>2.9899999999999999E-2</v>
+      </c>
+      <c r="N30" s="4">
+        <v>0.37240000000000001</v>
+      </c>
+      <c r="O30" s="4">
+        <v>0</v>
       </c>
       <c r="P30">
         <v>9</v>
@@ -3706,17 +2989,17 @@
       <c r="Q30">
         <v>0</v>
       </c>
-      <c r="R30" t="s">
-        <v>105</v>
-      </c>
-      <c r="S30" t="s">
-        <v>26</v>
+      <c r="R30" s="4">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="S30" s="4">
+        <v>0</v>
       </c>
       <c r="T30" s="1">
         <v>19822.881355932204</v>
       </c>
-      <c r="U30" t="s">
-        <v>27</v>
+      <c r="U30" s="1">
+        <v>0</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -3727,49 +3010,49 @@
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>331</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>331</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>305</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>305</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s">
-        <v>306</v>
-      </c>
-      <c r="F31" t="s">
-        <v>258</v>
+        <v>74</v>
+      </c>
+      <c r="F31" s="3">
+        <v>126</v>
       </c>
       <c r="G31">
         <v>5</v>
       </c>
-      <c r="H31" t="s">
-        <v>83</v>
-      </c>
-      <c r="I31" t="s">
-        <v>45</v>
-      </c>
-      <c r="J31" t="s">
-        <v>162</v>
+      <c r="H31" s="4">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="I31" s="4">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="J31" s="3">
+        <v>166</v>
       </c>
       <c r="K31">
         <v>6</v>
       </c>
-      <c r="L31" t="s">
-        <v>83</v>
-      </c>
-      <c r="M31" t="s">
-        <v>62</v>
-      </c>
-      <c r="N31" t="s">
-        <v>25</v>
-      </c>
-      <c r="O31" t="s">
-        <v>25</v>
+      <c r="L31" s="4">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="M31" s="4">
+        <v>1.9E-3</v>
+      </c>
+      <c r="N31" s="4">
+        <v>1</v>
+      </c>
+      <c r="O31" s="4">
+        <v>1</v>
       </c>
       <c r="P31">
         <v>6</v>
@@ -3777,17 +3060,17 @@
       <c r="Q31">
         <v>0</v>
       </c>
-      <c r="R31" t="s">
-        <v>307</v>
-      </c>
-      <c r="S31" t="s">
-        <v>26</v>
+      <c r="R31" s="4">
+        <v>4.7600000000000003E-2</v>
+      </c>
+      <c r="S31" s="4">
+        <v>0</v>
       </c>
       <c r="T31" s="1">
         <v>4316.9491525423728</v>
       </c>
-      <c r="U31" t="s">
-        <v>27</v>
+      <c r="U31" s="1">
+        <v>0</v>
       </c>
       <c r="V31">
         <v>6</v>
@@ -3798,49 +3081,49 @@
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>386</v>
+        <v>146</v>
       </c>
       <c r="B32" t="s">
-        <v>387</v>
+        <v>147</v>
       </c>
       <c r="C32" t="s">
-        <v>308</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>308</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s">
-        <v>309</v>
-      </c>
-      <c r="F32" t="s">
-        <v>310</v>
+        <v>76</v>
+      </c>
+      <c r="F32" s="3">
+        <v>318</v>
       </c>
       <c r="G32">
         <v>12</v>
       </c>
-      <c r="H32" t="s">
-        <v>84</v>
-      </c>
-      <c r="I32" t="s">
-        <v>39</v>
-      </c>
-      <c r="J32" t="s">
-        <v>73</v>
+      <c r="H32" s="4">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="I32" s="4">
+        <v>5.3E-3</v>
+      </c>
+      <c r="J32" s="3">
+        <v>412</v>
       </c>
       <c r="K32">
         <v>18</v>
       </c>
-      <c r="L32" t="s">
-        <v>40</v>
-      </c>
-      <c r="M32" t="s">
-        <v>112</v>
-      </c>
-      <c r="N32" t="s">
-        <v>25</v>
-      </c>
-      <c r="O32" t="s">
-        <v>25</v>
+      <c r="L32" s="4">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="M32" s="4">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="N32" s="4">
+        <v>1</v>
+      </c>
+      <c r="O32" s="4">
+        <v>1</v>
       </c>
       <c r="P32">
         <v>3</v>
@@ -3848,17 +3131,17 @@
       <c r="Q32">
         <v>2</v>
       </c>
-      <c r="R32" t="s">
-        <v>87</v>
-      </c>
-      <c r="S32" t="s">
-        <v>122</v>
+      <c r="R32" s="4">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="S32" s="4">
+        <v>0.16669999999999999</v>
       </c>
       <c r="T32" s="1">
         <v>5844.9152542372885</v>
       </c>
-      <c r="U32" t="s">
-        <v>311</v>
+      <c r="U32" s="1">
+        <v>4598</v>
       </c>
       <c r="V32">
         <v>3</v>
@@ -3869,49 +3152,49 @@
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>332</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>333</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s">
-        <v>137</v>
-      </c>
-      <c r="F33" t="s">
-        <v>140</v>
+        <v>20</v>
+      </c>
+      <c r="F33" s="3">
+        <v>74</v>
       </c>
       <c r="G33">
         <v>5</v>
       </c>
-      <c r="H33" t="s">
-        <v>50</v>
-      </c>
-      <c r="I33" t="s">
-        <v>45</v>
-      </c>
-      <c r="J33" t="s">
-        <v>123</v>
+      <c r="H33" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="I33" s="4">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="J33" s="3">
+        <v>102</v>
       </c>
       <c r="K33">
         <v>5</v>
       </c>
-      <c r="L33" t="s">
-        <v>50</v>
-      </c>
-      <c r="M33" t="s">
-        <v>60</v>
-      </c>
-      <c r="N33" t="s">
-        <v>312</v>
-      </c>
-      <c r="O33" t="s">
-        <v>125</v>
+      <c r="L33" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="M33" s="4">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="N33" s="4">
+        <v>0.81910000000000005</v>
+      </c>
+      <c r="O33" s="4">
+        <v>0.66669999999999996</v>
       </c>
       <c r="P33">
         <v>2</v>
@@ -3919,17 +3202,17 @@
       <c r="Q33">
         <v>0</v>
       </c>
-      <c r="R33" t="s">
-        <v>132</v>
-      </c>
-      <c r="S33" t="s">
-        <v>26</v>
+      <c r="R33" s="4">
+        <v>2.7E-2</v>
+      </c>
+      <c r="S33" s="4">
+        <v>0</v>
       </c>
       <c r="T33" s="1">
         <v>5159.3220338983056</v>
       </c>
-      <c r="U33" t="s">
-        <v>27</v>
+      <c r="U33" s="1">
+        <v>0</v>
       </c>
       <c r="V33">
         <v>2</v>
@@ -3940,49 +3223,49 @@
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>388</v>
+        <v>148</v>
       </c>
       <c r="B34" t="s">
-        <v>389</v>
+        <v>149</v>
       </c>
       <c r="C34" t="s">
-        <v>313</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>313</v>
+        <v>77</v>
       </c>
       <c r="E34" t="s">
-        <v>314</v>
-      </c>
-      <c r="F34" t="s">
-        <v>101</v>
+        <v>78</v>
+      </c>
+      <c r="F34" s="3">
+        <v>76</v>
       </c>
       <c r="G34">
         <v>4</v>
       </c>
-      <c r="H34" t="s">
-        <v>96</v>
-      </c>
-      <c r="I34" t="s">
-        <v>57</v>
-      </c>
-      <c r="J34" t="s">
-        <v>71</v>
+      <c r="H34" s="4">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1.8E-3</v>
+      </c>
+      <c r="J34" s="3">
+        <v>100</v>
       </c>
       <c r="K34">
         <v>4</v>
       </c>
-      <c r="L34" t="s">
-        <v>50</v>
-      </c>
-      <c r="M34" t="s">
-        <v>44</v>
-      </c>
-      <c r="N34" t="s">
-        <v>315</v>
-      </c>
-      <c r="O34" t="s">
-        <v>25</v>
+      <c r="L34" s="4">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="M34" s="4">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="N34" s="4">
+        <v>0.97670000000000001</v>
+      </c>
+      <c r="O34" s="4">
+        <v>1</v>
       </c>
       <c r="P34">
         <v>2</v>
@@ -3990,17 +3273,17 @@
       <c r="Q34">
         <v>0</v>
       </c>
-      <c r="R34" t="s">
-        <v>191</v>
-      </c>
-      <c r="S34" t="s">
-        <v>26</v>
+      <c r="R34" s="4">
+        <v>2.63E-2</v>
+      </c>
+      <c r="S34" s="4">
+        <v>0</v>
       </c>
       <c r="T34" s="1">
         <v>1269.4915254237289</v>
       </c>
-      <c r="U34" t="s">
-        <v>27</v>
+      <c r="U34" s="1">
+        <v>0</v>
       </c>
       <c r="V34">
         <v>2</v>
@@ -4011,49 +3294,49 @@
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>390</v>
+        <v>150</v>
       </c>
       <c r="B35" t="s">
-        <v>391</v>
+        <v>151</v>
       </c>
       <c r="C35" t="s">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="E35" t="s">
-        <v>317</v>
-      </c>
-      <c r="F35" t="s">
-        <v>90</v>
+        <v>80</v>
+      </c>
+      <c r="F35" s="3">
+        <v>7</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
-      <c r="H35" t="s">
-        <v>54</v>
-      </c>
-      <c r="I35" t="s">
-        <v>26</v>
-      </c>
-      <c r="J35" t="s">
-        <v>102</v>
+      <c r="H35" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>12</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
-      <c r="L35" t="s">
-        <v>54</v>
-      </c>
-      <c r="M35" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" t="s">
-        <v>25</v>
-      </c>
-      <c r="O35" t="s">
-        <v>26</v>
+      <c r="L35" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0</v>
+      </c>
+      <c r="N35" s="4">
+        <v>1</v>
+      </c>
+      <c r="O35" s="4">
+        <v>0</v>
       </c>
       <c r="P35">
         <v>2</v>
@@ -4061,17 +3344,17 @@
       <c r="Q35">
         <v>0</v>
       </c>
-      <c r="R35" t="s">
-        <v>318</v>
-      </c>
-      <c r="S35" t="s">
-        <v>26</v>
+      <c r="R35" s="4">
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="S35" s="4">
+        <v>0</v>
       </c>
       <c r="T35" s="1">
         <v>3355.4406779661022</v>
       </c>
-      <c r="U35" t="s">
-        <v>27</v>
+      <c r="U35" s="1">
+        <v>0</v>
       </c>
       <c r="V35">
         <v>2</v>
@@ -4082,49 +3365,49 @@
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>392</v>
+        <v>152</v>
       </c>
       <c r="B36" t="s">
-        <v>393</v>
+        <v>153</v>
       </c>
       <c r="C36" t="s">
-        <v>320</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>320</v>
+        <v>81</v>
       </c>
       <c r="E36" t="s">
-        <v>321</v>
-      </c>
-      <c r="F36" t="s">
-        <v>150</v>
+        <v>82</v>
+      </c>
+      <c r="F36" s="3">
+        <v>159</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
-      <c r="H36" t="s">
-        <v>120</v>
-      </c>
-      <c r="I36" t="s">
-        <v>48</v>
-      </c>
-      <c r="J36" t="s">
-        <v>319</v>
+      <c r="H36" s="4">
+        <v>1.4E-3</v>
+      </c>
+      <c r="I36" s="4">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="J36" s="3">
+        <v>193</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
-      <c r="L36" t="s">
-        <v>42</v>
-      </c>
-      <c r="M36" t="s">
-        <v>77</v>
-      </c>
-      <c r="N36" t="s">
-        <v>25</v>
-      </c>
-      <c r="O36" t="s">
-        <v>25</v>
+      <c r="L36" s="4">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="M36" s="4">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="N36" s="4">
+        <v>1</v>
+      </c>
+      <c r="O36" s="4">
+        <v>1</v>
       </c>
       <c r="P36">
         <v>1</v>
@@ -4132,17 +3415,17 @@
       <c r="Q36">
         <v>0</v>
       </c>
-      <c r="R36" t="s">
-        <v>35</v>
-      </c>
-      <c r="S36" t="s">
-        <v>26</v>
+      <c r="R36" s="4">
+        <v>6.3E-3</v>
+      </c>
+      <c r="S36" s="4">
+        <v>0</v>
       </c>
       <c r="T36" s="1">
         <v>4660.1694915254238</v>
       </c>
-      <c r="U36" t="s">
-        <v>27</v>
+      <c r="U36" s="1">
+        <v>0</v>
       </c>
       <c r="V36">
         <v>1</v>
@@ -4153,49 +3436,49 @@
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>394</v>
+        <v>154</v>
       </c>
       <c r="B37" t="s">
-        <v>395</v>
+        <v>155</v>
       </c>
       <c r="C37" t="s">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="E37" t="s">
-        <v>323</v>
-      </c>
-      <c r="F37" t="s">
-        <v>142</v>
+        <v>84</v>
+      </c>
+      <c r="F37" s="3">
+        <v>0</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
-      <c r="H37" t="s">
-        <v>26</v>
-      </c>
-      <c r="I37" t="s">
-        <v>26</v>
-      </c>
-      <c r="J37" t="s">
-        <v>142</v>
+      <c r="H37" s="4">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" t="s">
-        <v>26</v>
+      <c r="L37" s="4">
+        <v>0</v>
+      </c>
+      <c r="M37" s="4">
+        <v>0</v>
+      </c>
+      <c r="N37" s="4">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4">
+        <v>0</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -4203,17 +3486,17 @@
       <c r="Q37">
         <v>0</v>
       </c>
-      <c r="R37" t="s">
-        <v>26</v>
-      </c>
-      <c r="S37" t="s">
-        <v>26</v>
+      <c r="R37" s="4">
+        <v>0</v>
+      </c>
+      <c r="S37" s="4">
+        <v>0</v>
       </c>
       <c r="T37" s="1">
         <v>0</v>
       </c>
-      <c r="U37" t="s">
-        <v>27</v>
+      <c r="U37" s="1">
+        <v>0</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -4224,49 +3507,49 @@
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>336</v>
+        <v>96</v>
       </c>
       <c r="B38" t="s">
-        <v>337</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="D38" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="E38" t="s">
-        <v>161</v>
-      </c>
-      <c r="F38" t="s">
-        <v>104</v>
+        <v>24</v>
+      </c>
+      <c r="F38" s="3">
+        <v>248</v>
       </c>
       <c r="G38">
         <v>22</v>
       </c>
-      <c r="H38" t="s">
-        <v>66</v>
-      </c>
-      <c r="I38" t="s">
-        <v>296</v>
-      </c>
-      <c r="J38" t="s">
-        <v>55</v>
+      <c r="H38" s="4">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="I38" s="4">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="J38" s="3">
+        <v>340</v>
       </c>
       <c r="K38">
         <v>29</v>
       </c>
-      <c r="L38" t="s">
-        <v>45</v>
-      </c>
-      <c r="M38" t="s">
-        <v>133</v>
-      </c>
-      <c r="N38" t="s">
-        <v>324</v>
-      </c>
-      <c r="O38" t="s">
-        <v>26</v>
+      <c r="L38" s="4">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="M38" s="4">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="N38" s="4">
+        <v>5.6500000000000002E-2</v>
+      </c>
+      <c r="O38" s="4">
+        <v>0</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -4274,17 +3557,17 @@
       <c r="Q38">
         <v>0</v>
       </c>
-      <c r="R38" t="s">
-        <v>26</v>
-      </c>
-      <c r="S38" t="s">
-        <v>26</v>
+      <c r="R38" s="4">
+        <v>0</v>
+      </c>
+      <c r="S38" s="4">
+        <v>0</v>
       </c>
       <c r="T38" s="1">
         <v>0</v>
       </c>
-      <c r="U38" t="s">
-        <v>27</v>
+      <c r="U38" s="1">
+        <v>0</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -4295,49 +3578,49 @@
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>396</v>
+        <v>156</v>
       </c>
       <c r="B39" t="s">
-        <v>397</v>
+        <v>157</v>
       </c>
       <c r="C39" t="s">
-        <v>325</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>325</v>
+        <v>85</v>
       </c>
       <c r="E39" t="s">
-        <v>326</v>
-      </c>
-      <c r="F39" t="s">
-        <v>163</v>
+        <v>86</v>
+      </c>
+      <c r="F39" s="3">
+        <v>17</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
-      <c r="H39" t="s">
-        <v>54</v>
-      </c>
-      <c r="I39" t="s">
-        <v>26</v>
-      </c>
-      <c r="J39" t="s">
-        <v>145</v>
+      <c r="H39" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="I39" s="4">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3">
+        <v>21</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
-      <c r="L39" t="s">
-        <v>54</v>
-      </c>
-      <c r="M39" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" t="s">
-        <v>25</v>
-      </c>
-      <c r="O39" t="s">
-        <v>26</v>
+      <c r="L39" s="4">
+        <v>1E-4</v>
+      </c>
+      <c r="M39" s="4">
+        <v>0</v>
+      </c>
+      <c r="N39" s="4">
+        <v>1</v>
+      </c>
+      <c r="O39" s="4">
+        <v>0</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -4345,17 +3628,17 @@
       <c r="Q39">
         <v>0</v>
       </c>
-      <c r="R39" t="s">
-        <v>26</v>
-      </c>
-      <c r="S39" t="s">
-        <v>26</v>
+      <c r="R39" s="4">
+        <v>0</v>
+      </c>
+      <c r="S39" s="4">
+        <v>0</v>
       </c>
       <c r="T39" s="1">
         <v>0</v>
       </c>
-      <c r="U39" t="s">
-        <v>27</v>
+      <c r="U39" s="1">
+        <v>0</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -4366,16 +3649,16 @@
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>334</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>335</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="P40" s="2">
         <v>11</v>
@@ -4386,16 +3669,16 @@
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>336</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s">
-        <v>337</v>
+        <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="D41" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="P41" s="2">
         <v>7</v>
@@ -4406,16 +3689,16 @@
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>398</v>
+        <v>158</v>
       </c>
       <c r="B42" t="s">
-        <v>399</v>
+        <v>159</v>
       </c>
       <c r="C42" t="s">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="D42" t="s">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="P42" s="2">
         <v>3</v>
@@ -4426,16 +3709,16 @@
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>376</v>
+        <v>136</v>
       </c>
       <c r="B43" t="s">
-        <v>377</v>
+        <v>137</v>
       </c>
       <c r="C43" t="s">
-        <v>271</v>
+        <v>63</v>
       </c>
       <c r="D43" t="s">
-        <v>271</v>
+        <v>63</v>
       </c>
       <c r="P43" s="2">
         <v>3</v>
@@ -4446,16 +3729,16 @@
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>394</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
-        <v>395</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="D44" t="s">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="P44" s="2">
         <v>1</v>

--- a/data/ams_weekly_data/White_Mulberry/business_report_week7.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week7.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,117 +417,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/business_report_week7.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week7.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,117 +429,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/business_report_week7.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/business_report_week7.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,117 +417,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>
